--- a/校园招聘/制造业/消费电子／通信／智能设备/生产物流类/质量工程师/3_需重新出题/4轮_消费电子／通信／智能设备_质量工程师_需要重新出题.xlsx
+++ b/校园招聘/制造业/消费电子／通信／智能设备/生产物流类/质量工程师/3_需重新出题/4轮_消费电子／通信／智能设备_质量工程师_需要重新出题.xlsx
@@ -1,34 +1,249 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/risei/Downloads/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D3BD91D-DCAB-2A44-A6A3-B499E1C1A762}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="出题" sheetId="1" r:id="rId1"/>
+    <sheet name="出答案" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="28">
+  <si>
+    <t>问题</t>
+  </si>
+  <si>
+    <t>技能分类</t>
+  </si>
+  <si>
+    <t>技能</t>
+  </si>
+  <si>
+    <t>知识点</t>
+  </si>
+  <si>
+    <t>难度</t>
+  </si>
+  <si>
+    <t>行业</t>
+  </si>
+  <si>
+    <t>岗位</t>
+  </si>
+  <si>
+    <t>招聘场景</t>
+  </si>
+  <si>
+    <t>JD</t>
+  </si>
+  <si>
+    <t>提示词</t>
+  </si>
+  <si>
+    <t>在SMT贴片工序中，某关键焊点的尺寸测量数据长期呈现正态分布，但CPK值持续低于1.0，而Cpk值却高于1.3。请简述这说明了什么过程问题，并指出最应优先检查的现场因素。</t>
+  </si>
+  <si>
+    <t>制程质量控制</t>
+  </si>
+  <si>
+    <t>过程能力分析</t>
+  </si>
+  <si>
+    <t>过程能力不足判断</t>
+  </si>
+  <si>
+    <t>中等</t>
+  </si>
+  <si>
+    <t>消费电子通信智能设备制造业</t>
+  </si>
+  <si>
+    <t>质量工程师</t>
+  </si>
+  <si>
+    <t>校园招聘/社会招聘通用</t>
+  </si>
+  <si>
+    <t>某智能音箱产线连续30批的麦克风信噪比测试数据绘制直方图后，呈现明显右偏且存在孤立高位点（远高于主分布区间）。现场确认该高位点对应批次未更换任何物料和工艺参数。请结合电子元器件批次特性和制程波动特点，说明该直方图形态最可能揭示的质量根源，并解释为何不能仅依据规格上限判定其为合格批次。</t>
+  </si>
+  <si>
+    <t>质量数据分析</t>
+  </si>
+  <si>
+    <t>质量统计工具</t>
+  </si>
+  <si>
+    <t>直方图应用</t>
+  </si>
+  <si>
+    <t>困难</t>
+  </si>
+  <si>
+    <t>某智能手表产线发现屏幕贴合良率连续三周下降，质量团队收集了近100块屏幕的贴合间隙实测数据并绘制直方图，图形呈现双峰形态。请简述这种分布特征最可能反映的现场实际原因，以及你接下来会重点核查的两个环节。</t>
+  </si>
+  <si>
+    <t>一、岗位通用职责
+ 1. 理解电子制造质量对象并完成基础质量判定
+负责识别消费电子、通信设备和智能设备常见制造对象与质量风险，包括PCBA、电子元器件、结构件、连接器、整机装配、外观、功能测试、包装运输等，能够根据检验标准、缺陷等级和基础质量规则进行初步判定。
+ 2. 执行检验与抽样规则，保证判定一致性
+负责理解来料、制程、成品、出货等环节的基础检验要求，按AQL、检验项目、判定标准和抽样规则进行质量判定，识别漏检、误判和标准不一致风险。
+ 3. 运用基础质量数据工具识别问题趋势
+负责收集和分析不良率、良率、返修率、客诉率、PPM等基础质量数据，使用柏拉图、趋势图、直方图、散点图等工具识别主要问题和变化趋势，为质量改善提供数据依据。
+ 4. 参与质量问题记录、初步分析与改善跟进
+负责对来料、制程、试产、客户反馈中的质量问题进行事实记录、现象描述、初步分类和改善跟进。校招/初级只要求基础问题描述和简单原因分类；社招要求能独立推动8D、CAPA、MRB等闭环。
+ 二、方向职责
+ 方向一：DQE / 研发质量
+负责在设计开发阶段识别产品质量风险，参与DFMEA、设计评审、设计验证和样机失效分析，推动设计问题在量产前关闭。该方向更关注设计缺陷、验证覆盖、可靠性边界和客户/法规要求前置转化。
+ 方向二：PQE / 制程质量
+负责SMT、组装、测试、包装等量产过程质量控制，监控SPC、CPK、FPY、不良率等指标，处理制程异常，推动良率改善、防错设计和过程能力提升。
+ 方向三：SQE / 供应商质量
+负责供应商准入、来料质量、供应商过程审核、物料异常处理、供应商8D改善跟进和关键物料风险管理，保障核心物料质量稳定。
+ 方向四：CQE / 客户质量
+负责客户投诉、RMA/DOA、售后质量数据、客户审核问题和市场质量趋势分析，推动客户8D回复、重复问题预防和客户质量风险沟通。
+ 方向五：NPI / 项目质量
+负责EVT/DVT/PVT、试产和量产导入阶段的质量策划，识别设计、物料、工艺、测试和可靠性风险，推动试产质量问题关闭和转产准入。
+ 方向六：可靠性质量
+负责整机、模组、电子物料和结构件的可靠性验证，覆盖环境应力、机械应力、寿命、ESD、EMC、安规和合规测试，分析测试失效并推动设计、物料或工艺改进。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"你是一位经验丰富的资深面试官，拥有超过 10 年人才招聘经验。你尤其擅长从知识深度、逻辑思维以及实战能力等多个维度全面评估候选人。
+现在请依据以下要求，为【{{industry}}】行业下的【{{job}}】岗位的候选人精心准备【{{num}}】道视频面试题。
+关于目标行业下岗位的岗位描述：【{{JD}}】
+## 面试题要求
+- 题目类型：必须为简答题。
+- 内容相关性：题目内容要紧密围绕【{{category}}】技能分类下【{{skill}}】技能里的【{{knowledge}}】知识点展开。
+- 行业岗位适用性：题目需与【{{industry}}】行业下的【{{job}}】岗位职责高度适配，贴合该行业实际情况。
+- 招聘场景：题目应契合【{{scene}}】这一特定招聘场景。
+- 题目难度：全部设定为【{{level}}】难度，具体难度定义如下：
+    · 简单：考察应聘者能否正确识别、描述生产物流中常见的业务流程、术语和操作规范，是否清楚这些操作背后的基本逻辑。提问内容涉及流程认知与业务常识，无场景，纯基础考察。例如要求复述某类物料的出入库操作要点或解释某个作业术语的含义，如“先进先出原则在仓库中如何体现？”。建议作答时间控制在60秒内。字数控制在10～30字。
+    · 中等：考察应聘者是否知道在一个常规生产或仓储作业场景下，用何种方法处理异常或改善现状，解决机制是什么。提问内容涉及操作方法的实际运用，场景是日常工作中会遇到的典型情况，禁止涉及穷举、优劣势分析、系统性设计或冲突情况。如“当生产线的物料配送出现积压，导致线边仓爆满影响现场6S和作业动线时，你会怎么调整配送节拍或叫料方式来解决？”建议作答时间控制在90秒内。字数控制在30～60字。
+    · 困难：考察应聘者在复杂业务场景下的判断力和统筹能力。提问内容是一个具体的、两难的生产或物流局面，需要候选人说清楚先保什么、放什么，凭什么这么取舍，事后怎么收场。场景是车间或仓库里真实会发生的复杂情景。如“产线上正在跑的A产品突然要加大产量，但备好的料是按原计划供的，这时候插单和缺料的压力全压在了现场。你会从哪几个环节动手，怎么调整才能稳住交期又不让库存冒顶？说说你的思路和先动哪步后动哪步的理由。”建议作答时间控制在120秒内。字数控制在60～90字。
+- 题干长度：一个题目里只能有1个小问，禁止连环提问！使读题时间控制在30秒内，难度越低的题题干应越好理解。
+-易答性：
+1.禁用词：写代码、写出、编写、绘制、计算等一些口头无法表述的内容，确保候选人仅通过口头回答即可完成答题；
+2.不能出现让候选人讲述某一个软件的操作步骤；
+3.提问应该逻辑严谨，简单易懂，提出问题时需要模仿面试官在面试的口吻，不能过于生硬而让候选人不能明白题目的意思；
+4.编程题要给出规定的编程语言。
+- 内容限制：
+1.问题中的应用场景/条件不能是虚构的或者故事化的场景。语言上，类似“假设....”的提问是不被允许的。
+2.技术时效性：题干禁止问旧版本/早期版本的技术，涉及的技术场景必须是2022年之后在用的，但不必在题干中标注年份。
+3.问题中不能出现【{{industry}}】行业名称、【{{scene}}】特定招聘场景名称、【{{job}}】职位
+4.对于【通用行业】的知识点提问需要通用化，业务场景需要是各行各业的应聘者都能看懂的。
+5.所有的问题都是知识点面试问题，不能出行为化面试题
+6.尽量不要出现英文，能用中文的用中文表达！
+7.禁止出现事实、知识错误！
+8.禁止出现“请用一句话回答”这类强势粗暴的提问方法，可以说“请简述”“请简单说说”等
+## 输出规范要求
+- 若题目数量超过 1 道，要保证所有题目内容不重复，从不同主题或提问角度进行设计。
+- 严格以规范的 JSON 格式输出结果，不包含任何额外的文本说明。
+## 输出示例
+{{
+    ""questions"": [{{
+        ""question"": ""题目题干""，
+        ""level"": ""难度"",
+        ""time"": 建议答题时间，整数类型
+    }}]
+}}"</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 岗位通用职责：围绕汽车整车与零部件产品，从开发、试制、量产到售后反馈全过程识别质量风险，建立质量控制要求，推动质量问题分析、整改验证和持续改进。
+2. 过程质量方向：负责量产现场质量控制、过程巡检、首件确认、分层审核、变化点管理和不合格品处置，保障关键工序和产品特性稳定受控。
+3. 开发SQE方向：负责新项目阶段供应商质量准入、开发质量策划、样件与试制质量确认、PPAP认可和量产前供应商过程风险关闭，确保供应商具备稳定量产能力。
+4. 量产SQE方向：负责SOP后供应商来料质量、量产异常、供应商8D闭环、质量绩效评价、年度审核、飞行审核、变更管控和供应商持续改善。
+5. 先期质量方向：参与新车型或新零部件从设计到量产的质量策划，识别特殊特性和潜在失效风险，组织试制阶段质量评审、问题跟踪和量产放行准备。
+6. 客户质量方向：对接主机厂或客户质量需求，处理客户投诉、审核不符合项、退货索赔和市场质量问题，组织内部分析并推动整改按期关闭。
+7. 质量体系方向：推动ISO9001/IATF16949体系在汽车制造现场落地，组织内审、过程审核、产品审核和管理评审，跟踪审核问题与体系流程优化。
+8. 整车与产品评价方向：围绕整车、系统或零部件的外观、装配、功能、尺寸、感知质量和可靠性表现开展评价，输出问题清单、质量统计和改善建议。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>"你是一位经验丰富的资深面试官，拥有超过 10 年人才招聘经验。你尤其擅长从知识深度、逻辑思维以及实战能力等多个维度全面评估候选人。
+现在请依据以下要求，为面试【{{job}}】职位的候选人的视频面试题【{{Q}}】生成符合规则的参考答案。
+## 参考答案要求
+- 内容相关性：题目内容要紧密围绕【{{category}}】技能分类下【{{skill}}】技能里的【{{knowledge}}】知识点展开。
+- 岗位适用性：答案需与【{{{industry}}】行业的【{{job}}】岗位的工作范畴高度适配，仅从该岗位工作内容角度生成。禁止从技术的口径回答问题！！岗位工作内容参考：【{{JD}}】
+- 使用场景：答案应契合【{{scene}}】这一特定使用场景。
+- 内容与格式：每个题目的三层参考答案字数合计限制在300～600字，每个题目考察的都是一个岗位上某个技能的掌握程度，掌握程度分为三个层次，因此参考答案也需要分层生成。对第一层给出回答题干所需的基本操作要点、流程要求或业务常识}，内容严格对应题干，不要举例，不要超出题干所问的范围！对第二层给出给出这个场景下常见实用的2～4种作业方法或调整套路的分析，每种做法在什么情况下好用、什么情况下会出问题，哪种在当下最管用，方法要在保证时效性的基础上全面！分析要深入！对第三层给出这个知识点或场景下最最常出现的1个异常情况和1个复杂问题，以及每种情况的解决思路，输出时要结构化！小标题结构为：1个异常情况概要，具体情况，解决思路；1个复杂问题概要，具体问题，解决思路。
+参考答案约束：
+1.参考答案的内容必须严格对应岗位口径
+2.禁止出现代码块、符号等书面表达，所有类似内容必须用口语自然语言描述的形式代替
+3.禁止出现公式、计算等
+4.能用中文的用中文表达
+5.涉及的技术方法必须是2023年之后在用的，但相关时间信息不必出现在答案文本中
+6.禁止出现知识、事实错误！！
+常见的错误清单：{把相近概念混为一谈
+把局部实现写成通用规律
+把适用条件说错或漏掉前提
+把可选方案写成唯一答案
+数学/统计结论直接上升为业务结论
+边界值、分类、覆盖率类题目只答一半
+举例本身错误
+绝对化、法条化、一刀切表述}
+## 输出示例
+{{
+    ""questions"": [{{
+        ""question"": ""题目题干""，
+          ""answer1"":""参考答案-第一层"",
+          ""answer2"":""参考答案-第二层"",
+          ""answer3"":""参考答案-第三层""
+    }}]
+}}"</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4">
     <font>
-      <name val="Calibri"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <family val="4"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,81 +261,31 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -408,82 +573,161 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:M1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:J4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>问题</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>第一层</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>第二层</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>第三层</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>技能分类</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>知识点</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>难度</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>行业</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>岗位</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>招聘场景</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>JD</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>提示词</t>
-        </is>
+    <row r="1" spans="1:10">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="409.6">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="409.6">
+      <c r="A3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="409.6">
+      <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBACB16E-DE23-AC4E-944D-BC4EBECEA1E9}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="409.6">
+      <c r="A2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>